--- a/artfynd/A 3067-2025 artfynd.xlsx
+++ b/artfynd/A 3067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122587582</v>
+        <v>122587588</v>
       </c>
       <c r="B2" t="n">
-        <v>90804</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519184</v>
+        <v>519367</v>
       </c>
       <c r="R2" t="n">
-        <v>6704827</v>
+        <v>6704714</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122587588</v>
+        <v>122587582</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>90804</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519367</v>
+        <v>519184</v>
       </c>
       <c r="R3" t="n">
-        <v>6704714</v>
+        <v>6704827</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 3067-2025 artfynd.xlsx
+++ b/artfynd/A 3067-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>122587582</v>
       </c>
       <c r="B3" t="n">
-        <v>90804</v>
+        <v>90798</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 3067-2025 artfynd.xlsx
+++ b/artfynd/A 3067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122587588</v>
+        <v>122587582</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>90798</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519367</v>
+        <v>519184</v>
       </c>
       <c r="R2" t="n">
-        <v>6704714</v>
+        <v>6704827</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122587582</v>
+        <v>122587588</v>
       </c>
       <c r="B3" t="n">
-        <v>90798</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519184</v>
+        <v>519367</v>
       </c>
       <c r="R3" t="n">
-        <v>6704827</v>
+        <v>6704714</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 3067-2025 artfynd.xlsx
+++ b/artfynd/A 3067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122587582</v>
+        <v>122587588</v>
       </c>
       <c r="B2" t="n">
-        <v>90798</v>
+        <v>78657</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519184</v>
+        <v>519367</v>
       </c>
       <c r="R2" t="n">
-        <v>6704827</v>
+        <v>6704714</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122587588</v>
+        <v>122587582</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>90799</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519367</v>
+        <v>519184</v>
       </c>
       <c r="R3" t="n">
-        <v>6704714</v>
+        <v>6704827</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 3067-2025 artfynd.xlsx
+++ b/artfynd/A 3067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122587588</v>
+        <v>122587582</v>
       </c>
       <c r="B2" t="n">
-        <v>78657</v>
+        <v>90802</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519367</v>
+        <v>519184</v>
       </c>
       <c r="R2" t="n">
-        <v>6704714</v>
+        <v>6704827</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122587582</v>
+        <v>122587588</v>
       </c>
       <c r="B3" t="n">
-        <v>90799</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519184</v>
+        <v>519367</v>
       </c>
       <c r="R3" t="n">
-        <v>6704827</v>
+        <v>6704714</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 3067-2025 artfynd.xlsx
+++ b/artfynd/A 3067-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122587582</v>
       </c>
       <c r="B2" t="n">
-        <v>90905</v>
+        <v>90909</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122587588</v>
       </c>
       <c r="B3" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 3067-2025 artfynd.xlsx
+++ b/artfynd/A 3067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122587582</v>
+        <v>122587588</v>
       </c>
       <c r="B2" t="n">
-        <v>90909</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519184</v>
+        <v>519367</v>
       </c>
       <c r="R2" t="n">
-        <v>6704827</v>
+        <v>6704714</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122587588</v>
+        <v>122587582</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>90909</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519367</v>
+        <v>519184</v>
       </c>
       <c r="R3" t="n">
-        <v>6704714</v>
+        <v>6704827</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 3067-2025 artfynd.xlsx
+++ b/artfynd/A 3067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122587588</v>
+        <v>122587582</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>90909</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519367</v>
+        <v>519184</v>
       </c>
       <c r="R2" t="n">
-        <v>6704714</v>
+        <v>6704827</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122587582</v>
+        <v>122587588</v>
       </c>
       <c r="B3" t="n">
-        <v>90909</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519184</v>
+        <v>519367</v>
       </c>
       <c r="R3" t="n">
-        <v>6704827</v>
+        <v>6704714</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 3067-2025 artfynd.xlsx
+++ b/artfynd/A 3067-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122587582</v>
       </c>
       <c r="B2" t="n">
-        <v>90909</v>
+        <v>90917</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 3067-2025 artfynd.xlsx
+++ b/artfynd/A 3067-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -885,6 +885,995 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123275165</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kalkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>519313</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6704750</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123273779</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kalkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>519280</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6704764</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123275196</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kalkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>519305</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6704734</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123275211</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kalkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>519564</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6704679</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ca,</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123273716</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kalkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>519290</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6704745</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123275228</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kalkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>519577</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6704679</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123275141</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kalkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>519302</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6704752</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123275266</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kalkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>519593</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6704682</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ca.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123275203</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kalkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>519548</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6704577</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3067-2025 artfynd.xlsx
+++ b/artfynd/A 3067-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123275165</v>
+        <v>123275141</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519313</v>
+        <v>519302</v>
       </c>
       <c r="R4" t="n">
-        <v>6704750</v>
+        <v>6704752</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123273779</v>
+        <v>123275196</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1027,11 +1027,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1042,13 +1038,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519280</v>
+        <v>519305</v>
       </c>
       <c r="R5" t="n">
-        <v>6704764</v>
+        <v>6704734</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,19 +1089,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123275196</v>
+        <v>123273779</v>
       </c>
       <c r="B6" t="n">
         <v>98365</v>
@@ -1138,7 +1134,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1149,13 +1149,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519305</v>
+        <v>519280</v>
       </c>
       <c r="R6" t="n">
-        <v>6704734</v>
+        <v>6704764</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,19 +1200,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123275211</v>
+        <v>123275228</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1245,11 +1245,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1260,13 +1256,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519564</v>
+        <v>519577</v>
       </c>
       <c r="R7" t="n">
         <v>6704679</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1296,11 +1292,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ca,</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1439,7 +1430,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123275228</v>
+        <v>123275165</v>
       </c>
       <c r="B9" t="n">
         <v>98365</v>
@@ -1483,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519577</v>
+        <v>519313</v>
       </c>
       <c r="R9" t="n">
-        <v>6704679</v>
+        <v>6704750</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1546,7 +1537,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123275141</v>
+        <v>123275266</v>
       </c>
       <c r="B10" t="n">
         <v>98365</v>
@@ -1579,7 +1570,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1590,13 +1585,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519302</v>
+        <v>519593</v>
       </c>
       <c r="R10" t="n">
-        <v>6704752</v>
+        <v>6704682</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,6 +1621,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ca.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123275266</v>
+        <v>123275203</v>
       </c>
       <c r="B11" t="n">
         <v>98365</v>
@@ -1686,11 +1686,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1701,13 +1697,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519593</v>
+        <v>519548</v>
       </c>
       <c r="R11" t="n">
-        <v>6704682</v>
+        <v>6704577</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1737,11 +1733,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ca.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123275203</v>
+        <v>123275211</v>
       </c>
       <c r="B12" t="n">
         <v>98365</v>
@@ -1802,7 +1793,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1813,13 +1808,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519548</v>
+        <v>519564</v>
       </c>
       <c r="R12" t="n">
-        <v>6704577</v>
+        <v>6704679</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1849,6 +1844,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca,</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 3067-2025 artfynd.xlsx
+++ b/artfynd/A 3067-2025 artfynd.xlsx
@@ -994,7 +994,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123275196</v>
+        <v>123275266</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1027,7 +1027,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1038,13 +1042,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519305</v>
+        <v>519593</v>
       </c>
       <c r="R5" t="n">
-        <v>6704734</v>
+        <v>6704682</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,6 +1078,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ca.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1212,7 +1221,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123275228</v>
+        <v>123275196</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1256,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519577</v>
+        <v>519305</v>
       </c>
       <c r="R7" t="n">
-        <v>6704679</v>
+        <v>6704734</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1430,7 +1439,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123275165</v>
+        <v>123275228</v>
       </c>
       <c r="B9" t="n">
         <v>98365</v>
@@ -1474,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519313</v>
+        <v>519577</v>
       </c>
       <c r="R9" t="n">
-        <v>6704750</v>
+        <v>6704679</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1537,7 +1546,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123275266</v>
+        <v>123275203</v>
       </c>
       <c r="B10" t="n">
         <v>98365</v>
@@ -1570,11 +1579,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1585,13 +1590,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519593</v>
+        <v>519548</v>
       </c>
       <c r="R10" t="n">
-        <v>6704682</v>
+        <v>6704577</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1621,11 +1626,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ca.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123275203</v>
+        <v>123275165</v>
       </c>
       <c r="B11" t="n">
         <v>98365</v>
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519548</v>
+        <v>519313</v>
       </c>
       <c r="R11" t="n">
-        <v>6704577</v>
+        <v>6704750</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 3067-2025 artfynd.xlsx
+++ b/artfynd/A 3067-2025 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123275141</v>
+        <v>123275165</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519302</v>
+        <v>519313</v>
       </c>
       <c r="R4" t="n">
-        <v>6704752</v>
+        <v>6704750</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123275266</v>
+        <v>123275228</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,11 +1027,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1042,13 +1038,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519593</v>
+        <v>519577</v>
       </c>
       <c r="R5" t="n">
-        <v>6704682</v>
+        <v>6704679</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,11 +1074,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ca.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123273779</v>
+        <v>123273716</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,7 +1136,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1158,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519280</v>
+        <v>519290</v>
       </c>
       <c r="R6" t="n">
-        <v>6704764</v>
+        <v>6704745</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1221,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123275196</v>
+        <v>123273779</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,7 +1245,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1265,13 +1260,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519305</v>
+        <v>519280</v>
       </c>
       <c r="R7" t="n">
-        <v>6704734</v>
+        <v>6704764</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1316,22 +1311,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123273716</v>
+        <v>123275203</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,11 +1356,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1376,13 +1367,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519290</v>
+        <v>519548</v>
       </c>
       <c r="R8" t="n">
-        <v>6704745</v>
+        <v>6704577</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,22 +1418,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123275228</v>
+        <v>123275266</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,7 +1463,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -1483,13 +1478,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519577</v>
+        <v>519593</v>
       </c>
       <c r="R9" t="n">
-        <v>6704679</v>
+        <v>6704682</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,6 +1514,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123275203</v>
+        <v>123275196</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519548</v>
+        <v>519305</v>
       </c>
       <c r="R10" t="n">
-        <v>6704577</v>
+        <v>6704734</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123275165</v>
+        <v>123275211</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,7 +1686,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1697,13 +1701,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519313</v>
+        <v>519564</v>
       </c>
       <c r="R11" t="n">
-        <v>6704750</v>
+        <v>6704679</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1733,6 +1737,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ca,</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123275211</v>
+        <v>123275141</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1793,11 +1802,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1808,13 +1813,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519564</v>
+        <v>519302</v>
       </c>
       <c r="R12" t="n">
-        <v>6704679</v>
+        <v>6704752</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1844,11 +1849,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca,</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 3067-2025 artfynd.xlsx
+++ b/artfynd/A 3067-2025 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123275165</v>
+        <v>123273779</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,7 +920,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -931,13 +935,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519313</v>
+        <v>519280</v>
       </c>
       <c r="R4" t="n">
-        <v>6704750</v>
+        <v>6704764</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,22 +986,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123275228</v>
+        <v>123275211</v>
       </c>
       <c r="B5" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,7 +1031,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1038,13 +1046,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519577</v>
+        <v>519564</v>
       </c>
       <c r="R5" t="n">
         <v>6704679</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,6 +1082,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ca,</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,7 +1117,7 @@
         <v>123273716</v>
       </c>
       <c r="B6" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1212,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123273779</v>
+        <v>123275165</v>
       </c>
       <c r="B7" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,11 +1258,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1260,13 +1269,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519280</v>
+        <v>519313</v>
       </c>
       <c r="R7" t="n">
-        <v>6704764</v>
+        <v>6704750</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,22 +1320,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123275203</v>
+        <v>123275141</v>
       </c>
       <c r="B8" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519548</v>
+        <v>519302</v>
       </c>
       <c r="R8" t="n">
-        <v>6704577</v>
+        <v>6704752</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1433,7 +1442,7 @@
         <v>123275266</v>
       </c>
       <c r="B9" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1546,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123275196</v>
+        <v>123275203</v>
       </c>
       <c r="B10" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519305</v>
+        <v>519548</v>
       </c>
       <c r="R10" t="n">
-        <v>6704734</v>
+        <v>6704577</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1653,10 +1662,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123275211</v>
+        <v>123275228</v>
       </c>
       <c r="B11" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,11 +1695,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1701,13 +1706,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519564</v>
+        <v>519577</v>
       </c>
       <c r="R11" t="n">
         <v>6704679</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1737,11 +1742,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ca,</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123275141</v>
+        <v>123275196</v>
       </c>
       <c r="B12" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519302</v>
+        <v>519305</v>
       </c>
       <c r="R12" t="n">
-        <v>6704752</v>
+        <v>6704734</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 3067-2025 artfynd.xlsx
+++ b/artfynd/A 3067-2025 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123273779</v>
+        <v>123275141</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,11 +920,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -935,13 +931,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519280</v>
+        <v>519302</v>
       </c>
       <c r="R4" t="n">
-        <v>6704764</v>
+        <v>6704752</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,22 +982,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123275211</v>
+        <v>123275196</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,11 +1027,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1046,13 +1038,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519564</v>
+        <v>519305</v>
       </c>
       <c r="R5" t="n">
-        <v>6704679</v>
+        <v>6704734</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,11 +1074,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ca,</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123273716</v>
+        <v>123275211</v>
       </c>
       <c r="B6" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,7 +1136,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1162,13 +1149,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519290</v>
+        <v>519564</v>
       </c>
       <c r="R6" t="n">
-        <v>6704745</v>
+        <v>6704679</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,6 +1185,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ca,</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,22 +1205,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123275165</v>
+        <v>123273779</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,7 +1250,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1269,13 +1265,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519313</v>
+        <v>519280</v>
       </c>
       <c r="R7" t="n">
-        <v>6704750</v>
+        <v>6704764</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1320,22 +1316,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123275141</v>
+        <v>123275228</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519302</v>
+        <v>519577</v>
       </c>
       <c r="R8" t="n">
-        <v>6704752</v>
+        <v>6704679</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1439,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123275266</v>
+        <v>123273716</v>
       </c>
       <c r="B9" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,7 +1470,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1487,13 +1483,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519593</v>
+        <v>519290</v>
       </c>
       <c r="R9" t="n">
-        <v>6704682</v>
+        <v>6704745</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1523,11 +1519,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ca.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,12 +1534,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1558,7 +1549,7 @@
         <v>123275203</v>
       </c>
       <c r="B10" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1662,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123275228</v>
+        <v>123275165</v>
       </c>
       <c r="B11" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1706,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519577</v>
+        <v>519313</v>
       </c>
       <c r="R11" t="n">
-        <v>6704679</v>
+        <v>6704750</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1769,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123275196</v>
+        <v>123275266</v>
       </c>
       <c r="B12" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,7 +1793,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1813,13 +1808,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519305</v>
+        <v>519593</v>
       </c>
       <c r="R12" t="n">
-        <v>6704734</v>
+        <v>6704682</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1849,6 +1844,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 3067-2025 artfynd.xlsx
+++ b/artfynd/A 3067-2025 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123275228</v>
+        <v>123275211</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,7 +920,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -931,13 +935,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519577</v>
+        <v>519564</v>
       </c>
       <c r="R4" t="n">
         <v>6704679</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,6 +971,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ca,</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123275141</v>
+        <v>123273716</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,7 +1036,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1038,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519302</v>
+        <v>519290</v>
       </c>
       <c r="R5" t="n">
-        <v>6704752</v>
+        <v>6704745</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,22 +1102,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123275266</v>
+        <v>123275196</v>
       </c>
       <c r="B6" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,11 +1147,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1149,13 +1158,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519593</v>
+        <v>519305</v>
       </c>
       <c r="R6" t="n">
-        <v>6704682</v>
+        <v>6704734</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,11 +1194,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ca.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123275211</v>
+        <v>123275141</v>
       </c>
       <c r="B7" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,11 +1254,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1265,13 +1265,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519564</v>
+        <v>519302</v>
       </c>
       <c r="R7" t="n">
-        <v>6704679</v>
+        <v>6704752</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1301,11 +1301,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ca,</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123273716</v>
+        <v>123275203</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,11 +1361,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1381,13 +1372,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519290</v>
+        <v>519548</v>
       </c>
       <c r="R8" t="n">
-        <v>6704745</v>
+        <v>6704577</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,22 +1423,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123273779</v>
+        <v>123275165</v>
       </c>
       <c r="B9" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,11 +1468,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -1492,13 +1479,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519280</v>
+        <v>519313</v>
       </c>
       <c r="R9" t="n">
-        <v>6704764</v>
+        <v>6704750</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1543,22 +1530,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123275203</v>
+        <v>123275228</v>
       </c>
       <c r="B10" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1599,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519548</v>
+        <v>519577</v>
       </c>
       <c r="R10" t="n">
-        <v>6704577</v>
+        <v>6704679</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1662,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123275165</v>
+        <v>123273779</v>
       </c>
       <c r="B11" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,7 +1682,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1706,13 +1697,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519313</v>
+        <v>519280</v>
       </c>
       <c r="R11" t="n">
-        <v>6704750</v>
+        <v>6704764</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1757,22 +1748,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123275196</v>
+        <v>123275266</v>
       </c>
       <c r="B12" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,7 +1793,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1813,13 +1808,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519305</v>
+        <v>519593</v>
       </c>
       <c r="R12" t="n">
-        <v>6704734</v>
+        <v>6704682</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1849,6 +1844,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 3067-2025 artfynd.xlsx
+++ b/artfynd/A 3067-2025 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123275211</v>
+        <v>123273716</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519564</v>
+        <v>519290</v>
       </c>
       <c r="R4" t="n">
-        <v>6704679</v>
+        <v>6704745</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,11 +971,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ca,</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,22 +986,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123273716</v>
+        <v>123275228</v>
       </c>
       <c r="B5" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,11 +1031,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1051,13 +1042,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519290</v>
+        <v>519577</v>
       </c>
       <c r="R5" t="n">
-        <v>6704745</v>
+        <v>6704679</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,22 +1093,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123275196</v>
+        <v>123275203</v>
       </c>
       <c r="B6" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519305</v>
+        <v>519548</v>
       </c>
       <c r="R6" t="n">
-        <v>6704734</v>
+        <v>6704577</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123275141</v>
+        <v>123273779</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,7 +1245,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1265,13 +1260,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519302</v>
+        <v>519280</v>
       </c>
       <c r="R7" t="n">
-        <v>6704752</v>
+        <v>6704764</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1316,22 +1311,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123275203</v>
+        <v>123275196</v>
       </c>
       <c r="B8" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519548</v>
+        <v>519305</v>
       </c>
       <c r="R8" t="n">
-        <v>6704577</v>
+        <v>6704734</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1435,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123275165</v>
+        <v>123275141</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519313</v>
+        <v>519302</v>
       </c>
       <c r="R9" t="n">
-        <v>6704750</v>
+        <v>6704752</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1542,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123275228</v>
+        <v>123275165</v>
       </c>
       <c r="B10" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1586,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519577</v>
+        <v>519313</v>
       </c>
       <c r="R10" t="n">
-        <v>6704679</v>
+        <v>6704750</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1649,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123273779</v>
+        <v>123275266</v>
       </c>
       <c r="B11" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1684,7 +1679,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1697,13 +1692,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519280</v>
+        <v>519593</v>
       </c>
       <c r="R11" t="n">
-        <v>6704764</v>
+        <v>6704682</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1733,6 +1728,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ca.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,22 +1748,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123275266</v>
+        <v>123275211</v>
       </c>
       <c r="B12" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519593</v>
+        <v>519564</v>
       </c>
       <c r="R12" t="n">
-        <v>6704682</v>
+        <v>6704679</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ca.</t>
+          <t>Ca,</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 3067-2025 artfynd.xlsx
+++ b/artfynd/A 3067-2025 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123273716</v>
+        <v>123275203</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,11 +920,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -935,13 +931,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519290</v>
+        <v>519548</v>
       </c>
       <c r="R4" t="n">
-        <v>6704745</v>
+        <v>6704577</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,22 +982,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123275228</v>
+        <v>123275141</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519577</v>
+        <v>519302</v>
       </c>
       <c r="R5" t="n">
-        <v>6704679</v>
+        <v>6704752</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1105,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123275203</v>
+        <v>123275196</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,10 +1145,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519548</v>
+        <v>519305</v>
       </c>
       <c r="R6" t="n">
-        <v>6704577</v>
+        <v>6704734</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123273779</v>
+        <v>123275165</v>
       </c>
       <c r="B7" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,11 +1241,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1260,13 +1252,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519280</v>
+        <v>519313</v>
       </c>
       <c r="R7" t="n">
-        <v>6704764</v>
+        <v>6704750</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,22 +1303,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123275196</v>
+        <v>123273779</v>
       </c>
       <c r="B8" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,7 +1348,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1367,13 +1363,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519305</v>
+        <v>519280</v>
       </c>
       <c r="R8" t="n">
-        <v>6704734</v>
+        <v>6704764</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,22 +1414,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123275141</v>
+        <v>123275266</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1463,7 +1459,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -1474,13 +1474,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519302</v>
+        <v>519593</v>
       </c>
       <c r="R9" t="n">
-        <v>6704752</v>
+        <v>6704682</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1510,6 +1510,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,10 +1542,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123275165</v>
+        <v>123275228</v>
       </c>
       <c r="B10" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1581,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519313</v>
+        <v>519577</v>
       </c>
       <c r="R10" t="n">
-        <v>6704750</v>
+        <v>6704679</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1644,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123275266</v>
+        <v>123275211</v>
       </c>
       <c r="B11" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,7 +1684,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1692,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519593</v>
+        <v>519564</v>
       </c>
       <c r="R11" t="n">
-        <v>6704682</v>
+        <v>6704679</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,7 +1737,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ca.</t>
+          <t>Ca,</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123275211</v>
+        <v>123273716</v>
       </c>
       <c r="B12" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1795,7 +1800,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1808,13 +1813,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519564</v>
+        <v>519290</v>
       </c>
       <c r="R12" t="n">
-        <v>6704679</v>
+        <v>6704745</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1844,11 +1849,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca,</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,12 +1864,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 3067-2025 artfynd.xlsx
+++ b/artfynd/A 3067-2025 artfynd.xlsx
@@ -1649,7 +1649,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123275211</v>
+        <v>123273716</v>
       </c>
       <c r="B11" t="n">
         <v>98504</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519564</v>
+        <v>519290</v>
       </c>
       <c r="R11" t="n">
-        <v>6704679</v>
+        <v>6704745</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1733,11 +1733,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ca,</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,19 +1748,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123273716</v>
+        <v>123275211</v>
       </c>
       <c r="B12" t="n">
         <v>98504</v>
@@ -1800,7 +1795,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1813,13 +1808,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519290</v>
+        <v>519564</v>
       </c>
       <c r="R12" t="n">
-        <v>6704745</v>
+        <v>6704679</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1849,6 +1844,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca,</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,12 +1864,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 3067-2025 artfynd.xlsx
+++ b/artfynd/A 3067-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123275203</v>
+        <v>123273779</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,7 +920,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -931,13 +935,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519548</v>
+        <v>519280</v>
       </c>
       <c r="R4" t="n">
-        <v>6704577</v>
+        <v>6704764</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,22 +986,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123275141</v>
+        <v>123275228</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519302</v>
+        <v>519577</v>
       </c>
       <c r="R5" t="n">
-        <v>6704752</v>
+        <v>6704679</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123275196</v>
+        <v>123275211</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,7 +1138,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1145,13 +1153,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519305</v>
+        <v>519564</v>
       </c>
       <c r="R6" t="n">
-        <v>6704734</v>
+        <v>6704679</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,6 +1189,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ca,</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123275165</v>
+        <v>123275196</v>
       </c>
       <c r="B7" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519313</v>
+        <v>519305</v>
       </c>
       <c r="R7" t="n">
-        <v>6704750</v>
+        <v>6704734</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1315,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123273779</v>
+        <v>123275141</v>
       </c>
       <c r="B8" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,11 +1361,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1363,13 +1372,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519280</v>
+        <v>519302</v>
       </c>
       <c r="R8" t="n">
-        <v>6704764</v>
+        <v>6704752</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1414,22 +1423,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123275266</v>
+        <v>123275128</v>
       </c>
       <c r="B9" t="n">
-        <v>98504</v>
+        <v>56700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,35 +1447,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1474,13 +1483,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519593</v>
+        <v>519309</v>
       </c>
       <c r="R9" t="n">
-        <v>6704682</v>
+        <v>6704731</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,18 +1521,12 @@
           <t>2025-03-17</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ca.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1542,10 +1545,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123275228</v>
+        <v>123275165</v>
       </c>
       <c r="B10" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1586,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519577</v>
+        <v>519313</v>
       </c>
       <c r="R10" t="n">
-        <v>6704679</v>
+        <v>6704750</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1652,7 +1655,7 @@
         <v>123273716</v>
       </c>
       <c r="B11" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1760,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123275211</v>
+        <v>123275203</v>
       </c>
       <c r="B12" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1793,11 +1796,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1808,13 +1807,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519564</v>
+        <v>519548</v>
       </c>
       <c r="R12" t="n">
-        <v>6704679</v>
+        <v>6704577</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1844,11 +1843,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca,</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1873,6 +1867,122 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123275266</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kalkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>519593</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6704682</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ca.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3067-2025 artfynd.xlsx
+++ b/artfynd/A 3067-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123273779</v>
+        <v>123275203</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -920,11 +920,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -935,13 +931,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519280</v>
+        <v>519548</v>
       </c>
       <c r="R4" t="n">
-        <v>6704764</v>
+        <v>6704577</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,19 +982,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123275228</v>
+        <v>123273716</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1031,7 +1027,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1042,13 +1042,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519577</v>
+        <v>519290</v>
       </c>
       <c r="R5" t="n">
-        <v>6704679</v>
+        <v>6704745</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,12 +1093,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1221,7 +1221,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123275196</v>
+        <v>123275165</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519305</v>
+        <v>519313</v>
       </c>
       <c r="R7" t="n">
-        <v>6704734</v>
+        <v>6704750</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1328,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123275141</v>
+        <v>123275128</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,31 +1340,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1372,13 +1376,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519302</v>
+        <v>519309</v>
       </c>
       <c r="R8" t="n">
-        <v>6704752</v>
+        <v>6704731</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1416,7 +1420,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1435,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123275128</v>
+        <v>123275196</v>
       </c>
       <c r="B9" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,35 +1450,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1483,13 +1482,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519309</v>
+        <v>519305</v>
       </c>
       <c r="R9" t="n">
-        <v>6704731</v>
+        <v>6704734</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1527,6 +1526,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1545,7 +1545,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123275165</v>
+        <v>123273779</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1578,7 +1578,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1589,13 +1593,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519313</v>
+        <v>519280</v>
       </c>
       <c r="R10" t="n">
-        <v>6704750</v>
+        <v>6704764</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1640,19 +1644,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123273716</v>
+        <v>123275228</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1685,11 +1689,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1700,13 +1700,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519290</v>
+        <v>519577</v>
       </c>
       <c r="R11" t="n">
-        <v>6704745</v>
+        <v>6704679</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1751,19 +1751,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123275203</v>
+        <v>123275266</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -1796,7 +1796,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1807,13 +1811,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519548</v>
+        <v>519593</v>
       </c>
       <c r="R12" t="n">
-        <v>6704577</v>
+        <v>6704682</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1843,6 +1847,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,7 +1879,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123275266</v>
+        <v>123275141</v>
       </c>
       <c r="B13" t="n">
         <v>98079</v>
@@ -1903,11 +1912,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1918,13 +1923,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519593</v>
+        <v>519302</v>
       </c>
       <c r="R13" t="n">
-        <v>6704682</v>
+        <v>6704752</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1954,11 +1959,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ca.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 3067-2025 artfynd.xlsx
+++ b/artfynd/A 3067-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123275203</v>
+        <v>123275228</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519548</v>
+        <v>519577</v>
       </c>
       <c r="R4" t="n">
-        <v>6704577</v>
+        <v>6704679</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123273716</v>
+        <v>123275196</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1027,11 +1027,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1042,13 +1038,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519290</v>
+        <v>519305</v>
       </c>
       <c r="R5" t="n">
-        <v>6704745</v>
+        <v>6704734</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,19 +1089,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123275211</v>
+        <v>123273779</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1140,7 +1136,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1153,13 +1149,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519564</v>
+        <v>519280</v>
       </c>
       <c r="R6" t="n">
-        <v>6704679</v>
+        <v>6704764</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,11 +1185,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ca,</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,19 +1200,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123275165</v>
+        <v>123275266</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1254,7 +1245,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1265,13 +1260,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519313</v>
+        <v>519593</v>
       </c>
       <c r="R7" t="n">
-        <v>6704750</v>
+        <v>6704682</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1301,6 +1296,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ca.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123275128</v>
+        <v>123275211</v>
       </c>
       <c r="B8" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,35 +1340,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1376,13 +1376,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519309</v>
+        <v>519564</v>
       </c>
       <c r="R8" t="n">
-        <v>6704731</v>
+        <v>6704679</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1414,12 +1414,18 @@
           <t>2025-03-17</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca,</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1438,7 +1444,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123275196</v>
+        <v>123275141</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1482,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519305</v>
+        <v>519302</v>
       </c>
       <c r="R9" t="n">
-        <v>6704734</v>
+        <v>6704752</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1545,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123273779</v>
+        <v>123275128</v>
       </c>
       <c r="B10" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,35 +1563,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1593,13 +1599,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519280</v>
+        <v>519309</v>
       </c>
       <c r="R10" t="n">
-        <v>6704764</v>
+        <v>6704731</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1637,26 +1643,25 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123275228</v>
+        <v>123275203</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1700,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519577</v>
+        <v>519548</v>
       </c>
       <c r="R11" t="n">
-        <v>6704679</v>
+        <v>6704577</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1763,7 +1768,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123275266</v>
+        <v>123273716</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -1798,7 +1803,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1811,13 +1816,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519593</v>
+        <v>519290</v>
       </c>
       <c r="R12" t="n">
-        <v>6704682</v>
+        <v>6704745</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1847,11 +1852,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,19 +1867,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123275141</v>
+        <v>123275165</v>
       </c>
       <c r="B13" t="n">
         <v>98079</v>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519302</v>
+        <v>519313</v>
       </c>
       <c r="R13" t="n">
-        <v>6704752</v>
+        <v>6704750</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 3067-2025 artfynd.xlsx
+++ b/artfynd/A 3067-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>122587582</v>
       </c>
       <c r="B2" t="n">
-        <v>90917</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,42 +776,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122587588</v>
+        <v>123275128</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,13 +819,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519367</v>
+        <v>519309</v>
       </c>
       <c r="R3" t="n">
-        <v>6704714</v>
+        <v>6704731</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -854,12 +849,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,34 +863,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123275228</v>
+        <v>123273716</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,7 +909,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -931,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519577</v>
+        <v>519290</v>
       </c>
       <c r="R4" t="n">
-        <v>6704679</v>
+        <v>6704745</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,27 +975,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123275196</v>
+        <v>123273779</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,7 +1015,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1038,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519305</v>
+        <v>519280</v>
       </c>
       <c r="R5" t="n">
-        <v>6704734</v>
+        <v>6704764</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,27 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123273779</v>
+        <v>123275141</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,11 +1121,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1149,13 +1132,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519280</v>
+        <v>519302</v>
       </c>
       <c r="R6" t="n">
-        <v>6704764</v>
+        <v>6704752</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,27 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123275266</v>
+        <v>123275165</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,11 +1223,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1260,13 +1234,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519593</v>
+        <v>519313</v>
       </c>
       <c r="R7" t="n">
-        <v>6704682</v>
+        <v>6704750</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1296,11 +1270,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ca.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,15 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123275211</v>
+        <v>123275196</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,11 +1325,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1376,13 +1336,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519564</v>
+        <v>519305</v>
       </c>
       <c r="R8" t="n">
-        <v>6704679</v>
+        <v>6704734</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,11 +1372,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ca,</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,15 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123275141</v>
+        <v>123275203</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519302</v>
+        <v>519548</v>
       </c>
       <c r="R9" t="n">
-        <v>6704752</v>
+        <v>6704577</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1551,47 +1501,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123275128</v>
+        <v>123275211</v>
       </c>
       <c r="B10" t="n">
-        <v>56700</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1599,13 +1544,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519309</v>
+        <v>519564</v>
       </c>
       <c r="R10" t="n">
-        <v>6704731</v>
+        <v>6704679</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1637,12 +1582,18 @@
           <t>2025-03-17</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ca,</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1661,15 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123275203</v>
+        <v>123275228</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519548</v>
+        <v>519577</v>
       </c>
       <c r="R11" t="n">
-        <v>6704577</v>
+        <v>6704679</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1768,15 +1714,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123273716</v>
+        <v>123275266</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1744,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1816,13 +1757,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519290</v>
+        <v>519593</v>
       </c>
       <c r="R12" t="n">
-        <v>6704745</v>
+        <v>6704682</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1852,6 +1793,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,122 +1813,15 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>123275165</v>
-      </c>
-      <c r="B13" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Kalkberget, Dlr</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>519313</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6704750</v>
-      </c>
-      <c r="S13" t="n">
-        <v>5</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Borlänge</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Stora Tuna</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3067-2025 artfynd.xlsx
+++ b/artfynd/A 3067-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122587582</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123275128</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123273716</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123273779</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123275141</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123275165</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,6 +1431,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123275196</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123275203</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1609,6 +1654,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123275211</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1711,6 +1761,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123275228</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1822,8 +1877,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123275266</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>